--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Under\OneDrive\Рабочий стол\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vibe Coding\Test site\v-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DBE98F-2A33-4020-BF08-AE30C1E762EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF21C59A-F6C1-4FD4-B372-810C0517C259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Товары" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="43">
   <si>
     <t>Список</t>
   </si>
@@ -148,12 +148,36 @@
   <si>
     <t>Нет</t>
   </si>
+  <si>
+    <t>https://disk.yandex.ru/i/kRH3sWjGmfgIwA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/Q2AtFjNxgUiDgQ</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/s76QrodTurxqoA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/1By5PutprcsWvA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/tLBrBrEaMHtoKA</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/K0YA92yyNyjzMg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/qQG6vvRLCdG-bg</t>
+  </si>
+  <si>
+    <t>https://disk.yandex.ru/i/YNFKZaBx5ae-gg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -242,6 +266,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -363,10 +394,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -471,20 +503,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -775,7 +814,9 @@
       <c r="F2" s="40">
         <v>10</v>
       </c>
-      <c r="G2" s="21"/>
+      <c r="G2" s="44" t="s">
+        <v>35</v>
+      </c>
       <c r="H2" s="21" t="s">
         <v>32</v>
       </c>
@@ -809,7 +850,9 @@
       <c r="F3" s="40">
         <v>11</v>
       </c>
-      <c r="G3" s="27"/>
+      <c r="G3" s="45" t="s">
+        <v>36</v>
+      </c>
       <c r="H3" s="21" t="s">
         <v>32</v>
       </c>
@@ -845,7 +888,9 @@
       <c r="F4" s="40">
         <v>12</v>
       </c>
-      <c r="G4" s="27"/>
+      <c r="G4" s="45" t="s">
+        <v>37</v>
+      </c>
       <c r="H4" s="21" t="s">
         <v>32</v>
       </c>
@@ -878,7 +923,9 @@
       <c r="F5" s="40">
         <v>13</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="45" t="s">
+        <v>38</v>
+      </c>
       <c r="H5" s="21" t="s">
         <v>32</v>
       </c>
@@ -911,7 +958,9 @@
       <c r="F6" s="40">
         <v>14</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="45" t="s">
+        <v>39</v>
+      </c>
       <c r="H6" s="21" t="s">
         <v>32</v>
       </c>
@@ -944,7 +993,9 @@
       <c r="F7" s="40">
         <v>15</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="45" t="s">
+        <v>40</v>
+      </c>
       <c r="H7" s="21" t="s">
         <v>32</v>
       </c>
@@ -977,7 +1028,9 @@
       <c r="F8" s="40">
         <v>16</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="45" t="s">
+        <v>41</v>
+      </c>
       <c r="H8" s="21" t="s">
         <v>32</v>
       </c>
@@ -1010,7 +1063,9 @@
       <c r="F9" s="40">
         <v>17</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="45" t="s">
+        <v>42</v>
+      </c>
       <c r="H9" s="21" t="s">
         <v>32</v>
       </c>
@@ -12846,6 +12901,16 @@
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{F9C022B8-4238-44E8-AA00-91EA8DDCC177}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{0F753D52-3116-45EE-A77D-0C850C943536}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{A1EAE1B7-E96D-4635-88BB-396FF127DE6D}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{8E0C6CBD-F1AD-4B23-9D20-2C075C0B758D}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{C43E423C-D334-480A-8F05-972C3D2F4E2A}"/>
+    <hyperlink ref="G7" r:id="rId6" xr:uid="{4F3B71E5-F7E9-411D-8A95-F419A60C1215}"/>
+    <hyperlink ref="G8" r:id="rId7" xr:uid="{EF0A1A2E-DA1D-47BD-8733-056E21FE5E4D}"/>
+    <hyperlink ref="G9" r:id="rId8" xr:uid="{56833AF0-0AC1-4200-ADC5-EDE458641F43}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
